--- a/coding/descriptive/sample_descriptive.xlsx
+++ b/coding/descriptive/sample_descriptive.xlsx
@@ -1,23 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\01 DE\5. postdoc\SocEnRep Project\WP1 &amp; 2\litsearch\coding\descriptive\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57501EAD-D51C-40B5-A21D-1D26CED5D38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Ineke" sheetId="1" r:id="rId1"/>
-    <sheet name="Mehtab" sheetId="2" r:id="rId2"/>
-    <sheet name="Elisabetta" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="Ineke" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Mehtab" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Elisabetta" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="4inh/ZUyUppdOAP6hzYwIcQ1BePdGTP9WqWwFET9i+Y="/>
@@ -27,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="185">
   <si>
     <t>Ineke — Articles to Review</t>
   </si>
@@ -152,9 +143,6 @@
     <t>10.1257/jel.20171350</t>
   </si>
   <si>
-    <t>☐</t>
-  </si>
-  <si>
     <t>Thorpe, Brandon</t>
   </si>
   <si>
@@ -203,6 +191,9 @@
     <t>10.12688/f1000research.20843.1</t>
   </si>
   <si>
+    <t>Mehtab — Articles to Review</t>
+  </si>
+  <si>
     <t>Kim, Jenna; Blake, Catherine; Darch, Peter T.</t>
   </si>
   <si>
@@ -305,6 +296,9 @@
     <t>10.3789/niso-rp-31-2021</t>
   </si>
   <si>
+    <t>Elisabetta — Articles to Review</t>
+  </si>
+  <si>
     <t>Stewart, Andrew J.; Farran, Emily K.; Grange, James A. et al.</t>
   </si>
   <si>
@@ -579,83 +573,79 @@
   </si>
   <si>
     <t>10.1093/qopen/qoae031</t>
-  </si>
-  <si>
-    <t>Mehtab — Articles to Review</t>
-  </si>
-  <si>
-    <t>Elisabetta — Articles to Review</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="11">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font/>
+    <font>
+      <b/>
+      <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF467886"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="14.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF467886"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -663,35 +653,28 @@
         <bgColor rgb="FF356854"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
+    <border/>
     <border>
       <left/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -706,210 +689,190 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="18">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="4">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
           <bgColor rgb="FFF6F8F9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="3">
-    <tableStyle name="Ineke-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+    <tableStyle count="3" pivot="0" name="Ineke-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="Mehtab-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+    <tableStyle count="3" pivot="0" name="Mehtab-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="Elisabetta-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    <tableStyle count="3" pivot="0" name="Elisabetta-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A2:I47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No."/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Authors"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Year"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Source"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="DOI"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Google Drive"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Google Form Link"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Done"/>
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Authors" id="2"/>
+    <tableColumn name="Year" id="3"/>
+    <tableColumn name="Title" id="4"/>
+    <tableColumn name="Source" id="5"/>
+    <tableColumn name="DOI" id="6"/>
+    <tableColumn name="Google Drive" id="7"/>
+    <tableColumn name="Google Form Link" id="8"/>
+    <tableColumn name="Done" id="9"/>
   </tableColumns>
-  <tableStyleInfo name="Ineke-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Ineke-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A2:I47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No."/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Authors"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Year"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Title"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Source"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="DOI"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Google Drive"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Google Form Link"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Done"/>
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Authors" id="2"/>
+    <tableColumn name="Year" id="3"/>
+    <tableColumn name="Title" id="4"/>
+    <tableColumn name="Source" id="5"/>
+    <tableColumn name="DOI" id="6"/>
+    <tableColumn name="Google Drive" id="7"/>
+    <tableColumn name="Google Form Link" id="8"/>
+    <tableColumn name="Done" id="9"/>
   </tableColumns>
-  <tableStyleInfo name="Mehtab-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Mehtab-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A2:I47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="No."/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Authors"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Year"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Title"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Source"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="DOI"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Google Drive"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Google Form Link"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Done"/>
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Authors" id="2"/>
+    <tableColumn name="Year" id="3"/>
+    <tableColumn name="Title" id="4"/>
+    <tableColumn name="Source" id="5"/>
+    <tableColumn name="DOI" id="6"/>
+    <tableColumn name="Google Drive" id="7"/>
+    <tableColumn name="Google Form Link" id="8"/>
+    <tableColumn name="Done" id="9"/>
   </tableColumns>
-  <tableStyleInfo name="Elisabetta-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Elisabetta-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1099,1377 +1062,1375 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="4" max="4" width="59.21875" customWidth="1"/>
-    <col min="5" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.75"/>
+    <col customWidth="1" min="2" max="2" width="31.5"/>
+    <col customWidth="1" min="4" max="4" width="59.25"/>
+    <col customWidth="1" min="5" max="6" width="27.75"/>
+    <col customWidth="1" min="7" max="7" width="16.88"/>
+    <col customWidth="1" min="8" max="8" width="21.25"/>
+    <col customWidth="1" min="9" max="9" width="10.13"/>
+    <col customWidth="1" min="10" max="26" width="8.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" ht="24.0" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
-        <v>2015</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="6">
+        <v>2015.0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="G3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3">
-        <v>2016</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="6">
+        <v>2016.0</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A5" s="2">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="G4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A6" s="2">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="G5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A7" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A8" s="2">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="G7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A9" s="2">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="G8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="6">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="G9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A10" s="2">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="2">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A12" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="5">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A13" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A14" s="2">
+      <c r="G13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A15" s="2">
-        <v>31</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C15" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A16" s="2">
-        <v>33</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="G15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A17" s="2">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="G16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A18" s="2">
-        <v>45</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="G17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A19" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="G18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="5">
+        <v>47.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C19" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A20" s="2">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="G19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A21" s="2">
-        <v>54</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="G20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="12">
+        <v>2021.0</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A22" s="2">
-        <v>56</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="G21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="5">
+        <v>56.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A23" s="2">
-        <v>58</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="G22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="5">
+        <v>58.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="C23" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A24" s="2">
-        <v>59</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="F23" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="G23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="C24" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A25" s="2">
-        <v>64</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="F24" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="G24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="C25" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A26" s="2">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="F25" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="G25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="5">
+        <v>67.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="C26" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="2">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="F26" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="G26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="13">
+        <v>71.0</v>
+      </c>
+      <c r="B27" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="C27" s="14">
+        <v>2022.0</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A28" s="2">
-        <v>73</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="E27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="G27" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="5">
+        <v>73.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="C28" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A29" s="2">
-        <v>75</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="F28" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="G28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="5">
+        <v>75.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="C29" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="2">
-        <v>77</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="F29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="5">
+        <v>77.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="C30" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="2">
-        <v>84</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="F30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="G30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="5">
+        <v>84.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="C31" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A32" s="2">
-        <v>86</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="F31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="G31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="5">
+        <v>86.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="C32" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A33" s="2">
-        <v>91</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="F32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="G32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="5">
+        <v>91.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="C33" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A34" s="2">
-        <v>92</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="F33" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="G33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="5">
+        <v>92.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="C34" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A35" s="2">
-        <v>94</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="F34" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="G34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="5">
+        <v>94.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="C35" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="E35" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A36" s="2">
-        <v>99</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="F35" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="G35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="5">
+        <v>99.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="C36" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A37" s="2">
-        <v>100</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="F36" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="G36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="C37" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="E37" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A38" s="2">
-        <v>102</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="F37" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="G37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="5">
+        <v>102.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="C38" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A39" s="2">
-        <v>104</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="F38" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C39" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="G38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="5">
+        <v>104.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="C39" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="E39" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A40" s="2">
-        <v>108</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="F39" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="G39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="5">
+        <v>108.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="C40" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A41" s="2">
-        <v>112</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="F40" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C41" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D41" s="3" t="s">
+      <c r="G40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="5">
+        <v>112.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="C41" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="E41" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A42" s="2">
-        <v>116</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="F41" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="G41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="5">
+        <v>116.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="C42" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A43" s="2">
-        <v>118</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="F42" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="G42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="5">
+        <v>118.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="C43" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="E43" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A44" s="2">
-        <v>121</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="F43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C44" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="G43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="5">
+        <v>121.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="C44" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A45" s="2">
-        <v>126</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="F44" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D45" s="3" t="s">
+      <c r="G44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="5">
+        <v>126.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="C45" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="E45" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A46" s="2">
-        <v>128</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="F45" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C46" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="G45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="5">
+        <v>128.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="C46" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A47" s="2">
-        <v>132</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="F46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C47" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="G46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="5">
+        <v>132.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="C47" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="E47" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="14.25" customHeight="1"/>
+      <c r="F47" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -3427,1480 +3388,1482 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47">
       <formula1>"☐,☑"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47">
       <formula1>AND(ISNUMBER(A3),(NOT(OR(NOT(ISERROR(DATEVALUE(A3))), AND(ISNUMBER(A3), LEFT(CELL("format", A3))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G7" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G8" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G10" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H10" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G11" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H11" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G12" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H12" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G13" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H13" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G14" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H14" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="G15" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="H15" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="G16" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H16" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G17" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H17" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="G18" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H18" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="G19" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H19" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="G20" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H20" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="G21" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="H21" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="G22" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H22" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="G23" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H23" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="G24" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="H24" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="G25" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H25" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="G26" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H26" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="G27" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H27" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="G28" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H28" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="G29" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H29" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="G30" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="H30" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="G31" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="H31" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="G32" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="H32" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="G33" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="H33" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="G34" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="H34" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="G35" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="H35" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="G36" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="H36" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="G37" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="H37" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="G38" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="H38" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="G39" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="H39" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="G40" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="H40" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="G41" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="H41" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="G42" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="H42" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="G43" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="H43" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="G44" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="H44" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="G45" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="H45" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="G46" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="H46" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="G47" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="H47" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink r:id="rId1" ref="G3"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="G4"/>
+    <hyperlink r:id="rId4" ref="H4"/>
+    <hyperlink r:id="rId5" ref="G5"/>
+    <hyperlink r:id="rId6" ref="H5"/>
+    <hyperlink r:id="rId7" ref="G6"/>
+    <hyperlink r:id="rId8" ref="H6"/>
+    <hyperlink r:id="rId9" ref="G7"/>
+    <hyperlink r:id="rId10" ref="H7"/>
+    <hyperlink r:id="rId11" ref="G8"/>
+    <hyperlink r:id="rId12" ref="H8"/>
+    <hyperlink r:id="rId13" ref="G9"/>
+    <hyperlink r:id="rId14" ref="H9"/>
+    <hyperlink r:id="rId15" ref="G10"/>
+    <hyperlink r:id="rId16" ref="H10"/>
+    <hyperlink r:id="rId17" ref="G11"/>
+    <hyperlink r:id="rId18" ref="H11"/>
+    <hyperlink r:id="rId19" ref="G12"/>
+    <hyperlink r:id="rId20" ref="H12"/>
+    <hyperlink r:id="rId21" ref="G13"/>
+    <hyperlink r:id="rId22" ref="H13"/>
+    <hyperlink r:id="rId23" ref="G14"/>
+    <hyperlink r:id="rId24" ref="H14"/>
+    <hyperlink r:id="rId25" ref="G15"/>
+    <hyperlink r:id="rId26" ref="H15"/>
+    <hyperlink r:id="rId27" ref="G16"/>
+    <hyperlink r:id="rId28" ref="H16"/>
+    <hyperlink r:id="rId29" ref="G17"/>
+    <hyperlink r:id="rId30" ref="H17"/>
+    <hyperlink r:id="rId31" ref="G18"/>
+    <hyperlink r:id="rId32" ref="H18"/>
+    <hyperlink r:id="rId33" ref="G19"/>
+    <hyperlink r:id="rId34" ref="H19"/>
+    <hyperlink r:id="rId35" ref="G20"/>
+    <hyperlink r:id="rId36" ref="H20"/>
+    <hyperlink r:id="rId37" ref="G21"/>
+    <hyperlink r:id="rId38" ref="H21"/>
+    <hyperlink r:id="rId39" ref="G22"/>
+    <hyperlink r:id="rId40" ref="H22"/>
+    <hyperlink r:id="rId41" ref="G23"/>
+    <hyperlink r:id="rId42" ref="H23"/>
+    <hyperlink r:id="rId43" ref="G24"/>
+    <hyperlink r:id="rId44" ref="H24"/>
+    <hyperlink r:id="rId45" ref="G25"/>
+    <hyperlink r:id="rId46" ref="H25"/>
+    <hyperlink r:id="rId47" ref="G26"/>
+    <hyperlink r:id="rId48" ref="H26"/>
+    <hyperlink r:id="rId49" ref="G27"/>
+    <hyperlink r:id="rId50" ref="H27"/>
+    <hyperlink r:id="rId51" ref="G28"/>
+    <hyperlink r:id="rId52" ref="H28"/>
+    <hyperlink r:id="rId53" ref="G29"/>
+    <hyperlink r:id="rId54" ref="H29"/>
+    <hyperlink r:id="rId55" ref="G30"/>
+    <hyperlink r:id="rId56" ref="H30"/>
+    <hyperlink r:id="rId57" ref="G31"/>
+    <hyperlink r:id="rId58" ref="H31"/>
+    <hyperlink r:id="rId59" ref="G32"/>
+    <hyperlink r:id="rId60" ref="H32"/>
+    <hyperlink r:id="rId61" ref="G33"/>
+    <hyperlink r:id="rId62" ref="H33"/>
+    <hyperlink r:id="rId63" ref="G34"/>
+    <hyperlink r:id="rId64" ref="H34"/>
+    <hyperlink r:id="rId65" ref="G35"/>
+    <hyperlink r:id="rId66" ref="H35"/>
+    <hyperlink r:id="rId67" ref="G36"/>
+    <hyperlink r:id="rId68" ref="H36"/>
+    <hyperlink r:id="rId69" ref="G37"/>
+    <hyperlink r:id="rId70" ref="H37"/>
+    <hyperlink r:id="rId71" ref="G38"/>
+    <hyperlink r:id="rId72" ref="H38"/>
+    <hyperlink r:id="rId73" ref="G39"/>
+    <hyperlink r:id="rId74" ref="H39"/>
+    <hyperlink r:id="rId75" ref="G40"/>
+    <hyperlink r:id="rId76" ref="H40"/>
+    <hyperlink r:id="rId77" ref="G41"/>
+    <hyperlink r:id="rId78" ref="H41"/>
+    <hyperlink r:id="rId79" ref="G42"/>
+    <hyperlink r:id="rId80" ref="H42"/>
+    <hyperlink r:id="rId81" ref="G43"/>
+    <hyperlink r:id="rId82" ref="H43"/>
+    <hyperlink r:id="rId83" ref="G44"/>
+    <hyperlink r:id="rId84" ref="H44"/>
+    <hyperlink r:id="rId85" ref="G45"/>
+    <hyperlink r:id="rId86" ref="H45"/>
+    <hyperlink r:id="rId87" ref="G46"/>
+    <hyperlink r:id="rId88" ref="H46"/>
+    <hyperlink r:id="rId89" ref="G47"/>
+    <hyperlink r:id="rId90" ref="H47"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId91"/>
   <tableParts count="1">
-    <tablePart r:id="rId91"/>
+    <tablePart r:id="rId93"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="4" max="4" width="59.21875" customWidth="1"/>
-    <col min="5" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.75"/>
+    <col customWidth="1" min="2" max="2" width="31.5"/>
+    <col customWidth="1" min="4" max="4" width="59.25"/>
+    <col customWidth="1" min="5" max="6" width="27.75"/>
+    <col customWidth="1" min="7" max="7" width="16.88"/>
+    <col customWidth="1" min="8" max="8" width="21.25"/>
+    <col customWidth="1" min="9" max="9" width="10.13"/>
+    <col customWidth="1" min="10" max="26" width="8.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
+    <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2015.0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2016.0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="5">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="5">
+        <v>47.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="5">
+        <v>56.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="5">
+        <v>58.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="5">
+        <v>67.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="5">
+        <v>71.0</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="5">
+        <v>73.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="5">
+        <v>75.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="5">
+        <v>77.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="5">
+        <v>84.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="5">
+        <v>86.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="5">
+        <v>91.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="5">
+        <v>92.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="5">
+        <v>94.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="5">
+        <v>99.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="5">
+        <v>102.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="5">
+        <v>104.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="5">
+        <v>108.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="5">
+        <v>112.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="5">
+        <v>116.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="5">
+        <v>118.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="5">
+        <v>121.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="5">
+        <v>126.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="5">
+        <v>128.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="5">
+        <v>132.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2015</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2016</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A5" s="2">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A6" s="2">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A7" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A8" s="2">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A9" s="2">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A10" s="2">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="2">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A12" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A13" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A14" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A15" s="2">
-        <v>31</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A16" s="2">
-        <v>33</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A17" s="2">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A18" s="2">
-        <v>45</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A19" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A20" s="2">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A21" s="2">
-        <v>54</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A22" s="2">
-        <v>56</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A23" s="2">
-        <v>58</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A24" s="2">
-        <v>59</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A25" s="2">
-        <v>64</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A26" s="2">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="2">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A28" s="2">
-        <v>73</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A29" s="2">
-        <v>75</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="2">
-        <v>77</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="2">
-        <v>84</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A32" s="2">
-        <v>86</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A33" s="2">
-        <v>91</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A34" s="2">
-        <v>92</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A35" s="2">
-        <v>94</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A36" s="2">
-        <v>99</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A37" s="2">
-        <v>100</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A38" s="2">
-        <v>102</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A39" s="2">
-        <v>104</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A40" s="2">
-        <v>108</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C40" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A41" s="2">
-        <v>112</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A42" s="2">
-        <v>116</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A43" s="2">
-        <v>118</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C43" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A44" s="2">
-        <v>121</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C44" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A45" s="2">
-        <v>126</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C45" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A46" s="2">
-        <v>128</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C46" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A47" s="2">
-        <v>132</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C47" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="14.25" customHeight="1"/>
+      <c r="G47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -5858,1480 +5821,1482 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47">
       <formula1>"☐,☑"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47">
       <formula1>AND(ISNUMBER(A3),(NOT(OR(NOT(ISERROR(DATEVALUE(A3))), AND(ISNUMBER(A3), LEFT(CELL("format", A3))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="H4" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="H5" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="G6" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="H6" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="G7" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="H7" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="G8" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="H8" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="G9" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="H9" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="G10" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="H10" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="G11" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="H11" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="G12" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="H12" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="G13" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="H13" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="G14" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="H14" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="G15" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="H15" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="G16" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="H16" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="G17" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="H17" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="G18" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="H18" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="G19" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="H19" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="G20" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="H20" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="G21" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="H21" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="G22" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="H22" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="G23" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="H23" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="G24" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="H24" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="G25" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="H25" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="G26" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="H26" r:id="rId48" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="G27" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="H27" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="G28" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="H28" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="G29" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="H29" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="G30" r:id="rId55" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="H30" r:id="rId56" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="G31" r:id="rId57" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
-    <hyperlink ref="H31" r:id="rId58" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
-    <hyperlink ref="G32" r:id="rId59" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
-    <hyperlink ref="H32" r:id="rId60" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
-    <hyperlink ref="G33" r:id="rId61" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
-    <hyperlink ref="H33" r:id="rId62" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
-    <hyperlink ref="G34" r:id="rId63" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
-    <hyperlink ref="H34" r:id="rId64" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
-    <hyperlink ref="G35" r:id="rId65" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
-    <hyperlink ref="H35" r:id="rId66" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
-    <hyperlink ref="G36" r:id="rId67" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
-    <hyperlink ref="H36" r:id="rId68" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
-    <hyperlink ref="G37" r:id="rId69" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
-    <hyperlink ref="H37" r:id="rId70" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
-    <hyperlink ref="G38" r:id="rId71" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
-    <hyperlink ref="H38" r:id="rId72" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
-    <hyperlink ref="G39" r:id="rId73" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
-    <hyperlink ref="H39" r:id="rId74" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
-    <hyperlink ref="G40" r:id="rId75" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
-    <hyperlink ref="H40" r:id="rId76" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
-    <hyperlink ref="G41" r:id="rId77" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
-    <hyperlink ref="H41" r:id="rId78" xr:uid="{00000000-0004-0000-0100-00004D000000}"/>
-    <hyperlink ref="G42" r:id="rId79" xr:uid="{00000000-0004-0000-0100-00004E000000}"/>
-    <hyperlink ref="H42" r:id="rId80" xr:uid="{00000000-0004-0000-0100-00004F000000}"/>
-    <hyperlink ref="G43" r:id="rId81" xr:uid="{00000000-0004-0000-0100-000050000000}"/>
-    <hyperlink ref="H43" r:id="rId82" xr:uid="{00000000-0004-0000-0100-000051000000}"/>
-    <hyperlink ref="G44" r:id="rId83" xr:uid="{00000000-0004-0000-0100-000052000000}"/>
-    <hyperlink ref="H44" r:id="rId84" xr:uid="{00000000-0004-0000-0100-000053000000}"/>
-    <hyperlink ref="G45" r:id="rId85" xr:uid="{00000000-0004-0000-0100-000054000000}"/>
-    <hyperlink ref="H45" r:id="rId86" xr:uid="{00000000-0004-0000-0100-000055000000}"/>
-    <hyperlink ref="G46" r:id="rId87" xr:uid="{00000000-0004-0000-0100-000056000000}"/>
-    <hyperlink ref="H46" r:id="rId88" xr:uid="{00000000-0004-0000-0100-000057000000}"/>
-    <hyperlink ref="G47" r:id="rId89" xr:uid="{00000000-0004-0000-0100-000058000000}"/>
-    <hyperlink ref="H47" r:id="rId90" xr:uid="{00000000-0004-0000-0100-000059000000}"/>
+    <hyperlink r:id="rId1" ref="G3"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="G4"/>
+    <hyperlink r:id="rId4" ref="H4"/>
+    <hyperlink r:id="rId5" ref="G5"/>
+    <hyperlink r:id="rId6" ref="H5"/>
+    <hyperlink r:id="rId7" ref="G6"/>
+    <hyperlink r:id="rId8" ref="H6"/>
+    <hyperlink r:id="rId9" ref="G7"/>
+    <hyperlink r:id="rId10" ref="H7"/>
+    <hyperlink r:id="rId11" ref="G8"/>
+    <hyperlink r:id="rId12" ref="H8"/>
+    <hyperlink r:id="rId13" ref="G9"/>
+    <hyperlink r:id="rId14" ref="H9"/>
+    <hyperlink r:id="rId15" ref="G10"/>
+    <hyperlink r:id="rId16" ref="H10"/>
+    <hyperlink r:id="rId17" ref="G11"/>
+    <hyperlink r:id="rId18" ref="H11"/>
+    <hyperlink r:id="rId19" ref="G12"/>
+    <hyperlink r:id="rId20" ref="H12"/>
+    <hyperlink r:id="rId21" ref="G13"/>
+    <hyperlink r:id="rId22" ref="H13"/>
+    <hyperlink r:id="rId23" ref="G14"/>
+    <hyperlink r:id="rId24" ref="H14"/>
+    <hyperlink r:id="rId25" ref="G15"/>
+    <hyperlink r:id="rId26" ref="H15"/>
+    <hyperlink r:id="rId27" ref="G16"/>
+    <hyperlink r:id="rId28" ref="H16"/>
+    <hyperlink r:id="rId29" ref="G17"/>
+    <hyperlink r:id="rId30" ref="H17"/>
+    <hyperlink r:id="rId31" ref="G18"/>
+    <hyperlink r:id="rId32" ref="H18"/>
+    <hyperlink r:id="rId33" ref="G19"/>
+    <hyperlink r:id="rId34" ref="H19"/>
+    <hyperlink r:id="rId35" ref="G20"/>
+    <hyperlink r:id="rId36" ref="H20"/>
+    <hyperlink r:id="rId37" ref="G21"/>
+    <hyperlink r:id="rId38" ref="H21"/>
+    <hyperlink r:id="rId39" ref="G22"/>
+    <hyperlink r:id="rId40" ref="H22"/>
+    <hyperlink r:id="rId41" ref="G23"/>
+    <hyperlink r:id="rId42" ref="H23"/>
+    <hyperlink r:id="rId43" ref="G24"/>
+    <hyperlink r:id="rId44" ref="H24"/>
+    <hyperlink r:id="rId45" ref="G25"/>
+    <hyperlink r:id="rId46" ref="H25"/>
+    <hyperlink r:id="rId47" ref="G26"/>
+    <hyperlink r:id="rId48" ref="H26"/>
+    <hyperlink r:id="rId49" ref="G27"/>
+    <hyperlink r:id="rId50" ref="H27"/>
+    <hyperlink r:id="rId51" ref="G28"/>
+    <hyperlink r:id="rId52" ref="H28"/>
+    <hyperlink r:id="rId53" ref="G29"/>
+    <hyperlink r:id="rId54" ref="H29"/>
+    <hyperlink r:id="rId55" ref="G30"/>
+    <hyperlink r:id="rId56" ref="H30"/>
+    <hyperlink r:id="rId57" ref="G31"/>
+    <hyperlink r:id="rId58" ref="H31"/>
+    <hyperlink r:id="rId59" ref="G32"/>
+    <hyperlink r:id="rId60" ref="H32"/>
+    <hyperlink r:id="rId61" ref="G33"/>
+    <hyperlink r:id="rId62" ref="H33"/>
+    <hyperlink r:id="rId63" ref="G34"/>
+    <hyperlink r:id="rId64" ref="H34"/>
+    <hyperlink r:id="rId65" ref="G35"/>
+    <hyperlink r:id="rId66" ref="H35"/>
+    <hyperlink r:id="rId67" ref="G36"/>
+    <hyperlink r:id="rId68" ref="H36"/>
+    <hyperlink r:id="rId69" ref="G37"/>
+    <hyperlink r:id="rId70" ref="H37"/>
+    <hyperlink r:id="rId71" ref="G38"/>
+    <hyperlink r:id="rId72" ref="H38"/>
+    <hyperlink r:id="rId73" ref="G39"/>
+    <hyperlink r:id="rId74" ref="H39"/>
+    <hyperlink r:id="rId75" ref="G40"/>
+    <hyperlink r:id="rId76" ref="H40"/>
+    <hyperlink r:id="rId77" ref="G41"/>
+    <hyperlink r:id="rId78" ref="H41"/>
+    <hyperlink r:id="rId79" ref="G42"/>
+    <hyperlink r:id="rId80" ref="H42"/>
+    <hyperlink r:id="rId81" ref="G43"/>
+    <hyperlink r:id="rId82" ref="H43"/>
+    <hyperlink r:id="rId83" ref="G44"/>
+    <hyperlink r:id="rId84" ref="H44"/>
+    <hyperlink r:id="rId85" ref="G45"/>
+    <hyperlink r:id="rId86" ref="H45"/>
+    <hyperlink r:id="rId87" ref="G46"/>
+    <hyperlink r:id="rId88" ref="H46"/>
+    <hyperlink r:id="rId89" ref="G47"/>
+    <hyperlink r:id="rId90" ref="H47"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId91"/>
   <tableParts count="1">
-    <tablePart r:id="rId91"/>
+    <tablePart r:id="rId93"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="4" max="4" width="59.21875" customWidth="1"/>
-    <col min="5" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.75"/>
+    <col customWidth="1" min="2" max="2" width="31.5"/>
+    <col customWidth="1" min="4" max="4" width="59.25"/>
+    <col customWidth="1" min="5" max="6" width="27.75"/>
+    <col customWidth="1" min="7" max="7" width="16.88"/>
+    <col customWidth="1" min="8" max="8" width="21.25"/>
+    <col customWidth="1" min="9" max="9" width="10.13"/>
+    <col customWidth="1" min="10" max="26" width="8.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="1" ht="24.0" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
-        <v>2015</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="6">
+        <v>2015.0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="G3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2016.0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2016</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A5" s="2">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A6" s="2">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C10" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="5">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C15" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A7" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A8" s="2">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A9" s="2">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A10" s="2">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="2">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A12" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A13" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A14" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A15" s="2">
-        <v>31</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A16" s="2">
-        <v>33</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="G15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A17" s="2">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="G16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="6">
+        <v>2020.0</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A18" s="2">
-        <v>45</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="G17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A19" s="2">
-        <v>47</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="G18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="5">
+        <v>47.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C19" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A20" s="2">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="G19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A21" s="2">
-        <v>54</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="G20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A22" s="2">
-        <v>56</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="G21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="5">
+        <v>56.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A23" s="2">
-        <v>58</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="G22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="5">
+        <v>58.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="C23" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A24" s="2">
-        <v>59</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="F23" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="G23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="C24" s="6">
+        <v>2021.0</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A25" s="2">
-        <v>64</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="F24" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="G24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="C25" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A26" s="2">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="F25" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="G25" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="5">
+        <v>67.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="C26" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="2">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="F26" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="3">
-        <v>2022</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="G26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="5">
+        <v>71.0</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="C27" s="6">
+        <v>2022.0</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A28" s="2">
-        <v>73</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="E27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="G27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="5">
+        <v>73.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="C28" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A29" s="2">
-        <v>75</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="F28" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="G28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="5">
+        <v>75.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="C29" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="2">
-        <v>77</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="F29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="5">
+        <v>77.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="C30" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="2">
-        <v>84</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="F30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="G30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="5">
+        <v>84.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="C31" s="6">
+        <v>2023.0</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A32" s="2">
-        <v>86</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="F31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="G31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="5">
+        <v>86.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="C32" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A33" s="2">
-        <v>91</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="F32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="G32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="5">
+        <v>91.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="C33" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A34" s="2">
-        <v>92</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="F33" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="G33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="5">
+        <v>92.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="C34" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A35" s="2">
-        <v>94</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="F34" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="G34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="5">
+        <v>94.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="C35" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="E35" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A36" s="2">
-        <v>99</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="F35" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="G35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="5">
+        <v>99.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="C36" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A37" s="2">
-        <v>100</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="F36" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="G36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="C37" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="E37" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A38" s="2">
-        <v>102</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="F37" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="G37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="5">
+        <v>102.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="C38" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A39" s="2">
-        <v>104</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="F38" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C39" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="G38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="5">
+        <v>104.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="C39" s="6">
+        <v>2024.0</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="E39" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A40" s="2">
-        <v>108</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="F39" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="G39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="5">
+        <v>108.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="C40" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A41" s="2">
-        <v>112</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="F40" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C41" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D41" s="3" t="s">
+      <c r="G40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="5">
+        <v>112.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="C41" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="E41" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A42" s="2">
-        <v>116</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="F41" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="G41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="5">
+        <v>116.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="C42" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A43" s="2">
-        <v>118</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="F42" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="G42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="5">
+        <v>118.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="C43" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="E43" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A44" s="2">
-        <v>121</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="F43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C44" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="G43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="5">
+        <v>121.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="C44" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A45" s="2">
-        <v>126</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="F44" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D45" s="3" t="s">
+      <c r="G44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="5">
+        <v>126.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="C45" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="E45" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A46" s="2">
-        <v>128</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="F45" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C46" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="G45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="5">
+        <v>128.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="C46" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A47" s="2">
-        <v>132</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="F46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C47" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="G46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="5">
+        <v>132.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="C47" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="E47" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="14.25" customHeight="1"/>
+      <c r="F47" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -8289,110 +8254,112 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3:I47">
       <formula1>"☐,☑"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A3:A47 C3:C47">
       <formula1>AND(ISNUMBER(A3),(NOT(OR(NOT(ISERROR(DATEVALUE(A3))), AND(ISNUMBER(A3), LEFT(CELL("format", A3))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="H4" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="H5" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="G6" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="H6" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="G7" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="H7" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="G8" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="H8" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="G9" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="H9" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
-    <hyperlink ref="G10" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
-    <hyperlink ref="H10" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
-    <hyperlink ref="G11" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
-    <hyperlink ref="H11" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="G12" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
-    <hyperlink ref="H12" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
-    <hyperlink ref="G13" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
-    <hyperlink ref="H13" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
-    <hyperlink ref="G14" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
-    <hyperlink ref="H14" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
-    <hyperlink ref="G15" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
-    <hyperlink ref="H15" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
-    <hyperlink ref="G16" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
-    <hyperlink ref="H16" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
-    <hyperlink ref="G17" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
-    <hyperlink ref="H17" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
-    <hyperlink ref="G18" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
-    <hyperlink ref="H18" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
-    <hyperlink ref="G19" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
-    <hyperlink ref="H19" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
-    <hyperlink ref="G20" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
-    <hyperlink ref="H20" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
-    <hyperlink ref="G21" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
-    <hyperlink ref="H21" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
-    <hyperlink ref="G22" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
-    <hyperlink ref="H22" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
-    <hyperlink ref="G23" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
-    <hyperlink ref="H23" r:id="rId42" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
-    <hyperlink ref="G24" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
-    <hyperlink ref="H24" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
-    <hyperlink ref="G25" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
-    <hyperlink ref="H25" r:id="rId46" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
-    <hyperlink ref="G26" r:id="rId47" xr:uid="{00000000-0004-0000-0200-00002E000000}"/>
-    <hyperlink ref="H26" r:id="rId48" xr:uid="{00000000-0004-0000-0200-00002F000000}"/>
-    <hyperlink ref="G27" r:id="rId49" xr:uid="{00000000-0004-0000-0200-000030000000}"/>
-    <hyperlink ref="H27" r:id="rId50" xr:uid="{00000000-0004-0000-0200-000031000000}"/>
-    <hyperlink ref="G28" r:id="rId51" xr:uid="{00000000-0004-0000-0200-000032000000}"/>
-    <hyperlink ref="H28" r:id="rId52" xr:uid="{00000000-0004-0000-0200-000033000000}"/>
-    <hyperlink ref="G29" r:id="rId53" xr:uid="{00000000-0004-0000-0200-000034000000}"/>
-    <hyperlink ref="H29" r:id="rId54" xr:uid="{00000000-0004-0000-0200-000035000000}"/>
-    <hyperlink ref="G30" r:id="rId55" xr:uid="{00000000-0004-0000-0200-000036000000}"/>
-    <hyperlink ref="H30" r:id="rId56" xr:uid="{00000000-0004-0000-0200-000037000000}"/>
-    <hyperlink ref="G31" r:id="rId57" xr:uid="{00000000-0004-0000-0200-000038000000}"/>
-    <hyperlink ref="H31" r:id="rId58" xr:uid="{00000000-0004-0000-0200-000039000000}"/>
-    <hyperlink ref="G32" r:id="rId59" xr:uid="{00000000-0004-0000-0200-00003A000000}"/>
-    <hyperlink ref="H32" r:id="rId60" xr:uid="{00000000-0004-0000-0200-00003B000000}"/>
-    <hyperlink ref="G33" r:id="rId61" xr:uid="{00000000-0004-0000-0200-00003C000000}"/>
-    <hyperlink ref="H33" r:id="rId62" xr:uid="{00000000-0004-0000-0200-00003D000000}"/>
-    <hyperlink ref="G34" r:id="rId63" xr:uid="{00000000-0004-0000-0200-00003E000000}"/>
-    <hyperlink ref="H34" r:id="rId64" xr:uid="{00000000-0004-0000-0200-00003F000000}"/>
-    <hyperlink ref="G35" r:id="rId65" xr:uid="{00000000-0004-0000-0200-000040000000}"/>
-    <hyperlink ref="H35" r:id="rId66" xr:uid="{00000000-0004-0000-0200-000041000000}"/>
-    <hyperlink ref="G36" r:id="rId67" xr:uid="{00000000-0004-0000-0200-000042000000}"/>
-    <hyperlink ref="H36" r:id="rId68" xr:uid="{00000000-0004-0000-0200-000043000000}"/>
-    <hyperlink ref="G37" r:id="rId69" xr:uid="{00000000-0004-0000-0200-000044000000}"/>
-    <hyperlink ref="H37" r:id="rId70" xr:uid="{00000000-0004-0000-0200-000045000000}"/>
-    <hyperlink ref="G38" r:id="rId71" xr:uid="{00000000-0004-0000-0200-000046000000}"/>
-    <hyperlink ref="H38" r:id="rId72" xr:uid="{00000000-0004-0000-0200-000047000000}"/>
-    <hyperlink ref="G39" r:id="rId73" xr:uid="{00000000-0004-0000-0200-000048000000}"/>
-    <hyperlink ref="H39" r:id="rId74" xr:uid="{00000000-0004-0000-0200-000049000000}"/>
-    <hyperlink ref="G40" r:id="rId75" xr:uid="{00000000-0004-0000-0200-00004A000000}"/>
-    <hyperlink ref="H40" r:id="rId76" xr:uid="{00000000-0004-0000-0200-00004B000000}"/>
-    <hyperlink ref="G41" r:id="rId77" xr:uid="{00000000-0004-0000-0200-00004C000000}"/>
-    <hyperlink ref="H41" r:id="rId78" xr:uid="{00000000-0004-0000-0200-00004D000000}"/>
-    <hyperlink ref="G42" r:id="rId79" xr:uid="{00000000-0004-0000-0200-00004E000000}"/>
-    <hyperlink ref="H42" r:id="rId80" xr:uid="{00000000-0004-0000-0200-00004F000000}"/>
-    <hyperlink ref="G43" r:id="rId81" xr:uid="{00000000-0004-0000-0200-000050000000}"/>
-    <hyperlink ref="H43" r:id="rId82" xr:uid="{00000000-0004-0000-0200-000051000000}"/>
-    <hyperlink ref="G44" r:id="rId83" xr:uid="{00000000-0004-0000-0200-000052000000}"/>
-    <hyperlink ref="H44" r:id="rId84" xr:uid="{00000000-0004-0000-0200-000053000000}"/>
-    <hyperlink ref="G45" r:id="rId85" xr:uid="{00000000-0004-0000-0200-000054000000}"/>
-    <hyperlink ref="H45" r:id="rId86" xr:uid="{00000000-0004-0000-0200-000055000000}"/>
-    <hyperlink ref="G46" r:id="rId87" xr:uid="{00000000-0004-0000-0200-000056000000}"/>
-    <hyperlink ref="H46" r:id="rId88" xr:uid="{00000000-0004-0000-0200-000057000000}"/>
-    <hyperlink ref="G47" r:id="rId89" xr:uid="{00000000-0004-0000-0200-000058000000}"/>
-    <hyperlink ref="H47" r:id="rId90" xr:uid="{00000000-0004-0000-0200-000059000000}"/>
+    <hyperlink r:id="rId1" ref="G3"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="G4"/>
+    <hyperlink r:id="rId4" ref="H4"/>
+    <hyperlink r:id="rId5" ref="G5"/>
+    <hyperlink r:id="rId6" ref="H5"/>
+    <hyperlink r:id="rId7" ref="G6"/>
+    <hyperlink r:id="rId8" ref="H6"/>
+    <hyperlink r:id="rId9" ref="G7"/>
+    <hyperlink r:id="rId10" ref="H7"/>
+    <hyperlink r:id="rId11" ref="G8"/>
+    <hyperlink r:id="rId12" ref="H8"/>
+    <hyperlink r:id="rId13" ref="G9"/>
+    <hyperlink r:id="rId14" ref="H9"/>
+    <hyperlink r:id="rId15" ref="G10"/>
+    <hyperlink r:id="rId16" ref="H10"/>
+    <hyperlink r:id="rId17" ref="G11"/>
+    <hyperlink r:id="rId18" ref="H11"/>
+    <hyperlink r:id="rId19" ref="G12"/>
+    <hyperlink r:id="rId20" ref="H12"/>
+    <hyperlink r:id="rId21" ref="G13"/>
+    <hyperlink r:id="rId22" ref="H13"/>
+    <hyperlink r:id="rId23" ref="G14"/>
+    <hyperlink r:id="rId24" ref="H14"/>
+    <hyperlink r:id="rId25" ref="G15"/>
+    <hyperlink r:id="rId26" ref="H15"/>
+    <hyperlink r:id="rId27" ref="G16"/>
+    <hyperlink r:id="rId28" ref="H16"/>
+    <hyperlink r:id="rId29" ref="G17"/>
+    <hyperlink r:id="rId30" ref="H17"/>
+    <hyperlink r:id="rId31" ref="G18"/>
+    <hyperlink r:id="rId32" ref="H18"/>
+    <hyperlink r:id="rId33" ref="G19"/>
+    <hyperlink r:id="rId34" ref="H19"/>
+    <hyperlink r:id="rId35" ref="G20"/>
+    <hyperlink r:id="rId36" ref="H20"/>
+    <hyperlink r:id="rId37" ref="G21"/>
+    <hyperlink r:id="rId38" ref="H21"/>
+    <hyperlink r:id="rId39" ref="G22"/>
+    <hyperlink r:id="rId40" ref="H22"/>
+    <hyperlink r:id="rId41" ref="G23"/>
+    <hyperlink r:id="rId42" ref="H23"/>
+    <hyperlink r:id="rId43" ref="G24"/>
+    <hyperlink r:id="rId44" ref="H24"/>
+    <hyperlink r:id="rId45" ref="G25"/>
+    <hyperlink r:id="rId46" ref="H25"/>
+    <hyperlink r:id="rId47" ref="G26"/>
+    <hyperlink r:id="rId48" ref="H26"/>
+    <hyperlink r:id="rId49" ref="G27"/>
+    <hyperlink r:id="rId50" ref="H27"/>
+    <hyperlink r:id="rId51" ref="G28"/>
+    <hyperlink r:id="rId52" ref="H28"/>
+    <hyperlink r:id="rId53" ref="G29"/>
+    <hyperlink r:id="rId54" ref="H29"/>
+    <hyperlink r:id="rId55" ref="G30"/>
+    <hyperlink r:id="rId56" ref="H30"/>
+    <hyperlink r:id="rId57" ref="G31"/>
+    <hyperlink r:id="rId58" ref="H31"/>
+    <hyperlink r:id="rId59" ref="G32"/>
+    <hyperlink r:id="rId60" ref="H32"/>
+    <hyperlink r:id="rId61" ref="G33"/>
+    <hyperlink r:id="rId62" ref="H33"/>
+    <hyperlink r:id="rId63" ref="G34"/>
+    <hyperlink r:id="rId64" ref="H34"/>
+    <hyperlink r:id="rId65" ref="G35"/>
+    <hyperlink r:id="rId66" ref="H35"/>
+    <hyperlink r:id="rId67" ref="G36"/>
+    <hyperlink r:id="rId68" ref="H36"/>
+    <hyperlink r:id="rId69" ref="G37"/>
+    <hyperlink r:id="rId70" ref="H37"/>
+    <hyperlink r:id="rId71" ref="G38"/>
+    <hyperlink r:id="rId72" ref="H38"/>
+    <hyperlink r:id="rId73" ref="G39"/>
+    <hyperlink r:id="rId74" ref="H39"/>
+    <hyperlink r:id="rId75" ref="G40"/>
+    <hyperlink r:id="rId76" ref="H40"/>
+    <hyperlink r:id="rId77" ref="G41"/>
+    <hyperlink r:id="rId78" ref="H41"/>
+    <hyperlink r:id="rId79" ref="G42"/>
+    <hyperlink r:id="rId80" ref="H42"/>
+    <hyperlink r:id="rId81" ref="G43"/>
+    <hyperlink r:id="rId82" ref="H43"/>
+    <hyperlink r:id="rId83" ref="G44"/>
+    <hyperlink r:id="rId84" ref="H44"/>
+    <hyperlink r:id="rId85" ref="G45"/>
+    <hyperlink r:id="rId86" ref="H45"/>
+    <hyperlink r:id="rId87" ref="G46"/>
+    <hyperlink r:id="rId88" ref="H46"/>
+    <hyperlink r:id="rId89" ref="G47"/>
+    <hyperlink r:id="rId90" ref="H47"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId91"/>
   <tableParts count="1">
-    <tablePart r:id="rId91"/>
+    <tablePart r:id="rId93"/>
   </tableParts>
 </worksheet>
 </file>
--- a/coding/descriptive/sample_descriptive.xlsx
+++ b/coding/descriptive/sample_descriptive.xlsx
@@ -23,6 +23,12 @@
     <t>Ineke — Articles to Review</t>
   </si>
   <si>
+    <t>Mehtab — Articles to Review</t>
+  </si>
+  <si>
+    <t>Elisabetta — Articles to Review</t>
+  </si>
+  <si>
     <t>No.</t>
   </si>
   <si>
@@ -191,9 +197,6 @@
     <t>10.12688/f1000research.20843.1</t>
   </si>
   <si>
-    <t>Mehtab — Articles to Review</t>
-  </si>
-  <si>
     <t>Kim, Jenna; Blake, Catherine; Darch, Peter T.</t>
   </si>
   <si>
@@ -294,9 +297,6 @@
   </si>
   <si>
     <t>10.3789/niso-rp-31-2021</t>
-  </si>
-  <si>
-    <t>Elisabetta — Articles to Review</t>
   </si>
   <si>
     <t>Stewart, Andrew J.; Farran, Emily K.; Grange, James A. et al.</t>
@@ -591,6 +591,12 @@
       <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
     <font/>
     <font>
@@ -622,12 +628,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="14.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF467886"/>
@@ -640,7 +640,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,12 +651,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF356854"/>
         <bgColor rgb="FF356854"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -701,19 +695,19 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -721,28 +715,28 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,12 +788,12 @@
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Mehtab-style">
+    <tableStyle count="3" pivot="0" name="Elisabetta-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Elisabetta-style">
+    <tableStyle count="3" pivot="0" name="Mehtab-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -838,7 +832,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_3" name="Table_3" id="2">
   <tableColumns count="9">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Authors" id="2"/>
@@ -855,7 +849,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A2:I47" displayName="Table_2" name="Table_2" id="3">
   <tableColumns count="9">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Authors" id="2"/>
@@ -1087,738 +1081,738 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>3.0</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7">
         <v>2015.0</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>16</v>
+      <c r="G3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>4.0</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7">
         <v>2016.0</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>8.0</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
         <v>2017.0</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>9.0</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="7">
         <v>2017.0</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="6">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="6">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="6">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="6">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="6">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C15" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2018.0</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="5">
-        <v>21.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="5">
-        <v>23.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="5">
-        <v>31.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="F15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="6">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="7">
         <v>2020.0</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="5">
-        <v>33.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="D16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="7">
         <v>2020.0</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="5">
-        <v>34.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2020.0</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
+      <c r="F17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>45.0</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>47.0</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
+      <c r="F19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>51.0</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="6">
+      <c r="B20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
+      <c r="F20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>54.0</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>84</v>
+      <c r="B21" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="C21" s="12">
         <v>2021.0</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>16</v>
+      <c r="F21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>56.0</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="B22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
+      <c r="F22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>58.0</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
+      <c r="G23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>59.0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>2021.0</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
+      <c r="G24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>64.0</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>2022.0</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
+      <c r="G25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>67.0</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>2022.0</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
+      <c r="G26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -1841,593 +1835,593 @@
         <v>111</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="6">
         <v>73.0</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>2023.0</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="6" t="s">
+      <c r="E28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
+      <c r="G28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="6">
         <v>75.0</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>2023.0</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
+      <c r="G29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="6">
         <v>77.0</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="B30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="7">
         <v>2023.0</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
+      <c r="G30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="6">
         <v>84.0</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>2023.0</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>16</v>
+      <c r="G31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="6">
         <v>86.0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
+      <c r="G32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>91.0</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="6" t="s">
+      <c r="E33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
+      <c r="G33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>92.0</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
+      <c r="G34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>94.0</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
+      <c r="G35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>99.0</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="6" t="s">
+      <c r="E36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
+      <c r="G36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>100.0</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>16</v>
+      <c r="G37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>102.0</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="6" t="s">
+      <c r="E38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>16</v>
+      <c r="G38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>104.0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="7">
         <v>2024.0</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>16</v>
+      <c r="G39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>108.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G40" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>16</v>
+      <c r="G40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="6">
         <v>112.0</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G41" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>16</v>
+      <c r="G41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="6">
         <v>116.0</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="6" t="s">
+      <c r="E42" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="G42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>16</v>
+      <c r="G42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="6">
         <v>118.0</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>16</v>
+      <c r="G43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>121.0</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="G44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>16</v>
+      <c r="G44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="6">
         <v>126.0</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>16</v>
+      <c r="G45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="6">
         <v>128.0</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>16</v>
+      <c r="G46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="6">
         <v>132.0</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>16</v>
+      <c r="G47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1"/>
@@ -3517,1350 +3511,1350 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2016.0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="6">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="6">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="6">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="6">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2015.0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6">
-        <v>2016.0</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="5">
-        <v>9.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="6">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C15" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2018.0</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="5">
-        <v>21.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="5">
-        <v>23.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="5">
-        <v>31.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="F15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="6">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="7">
         <v>2020.0</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="5">
-        <v>33.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="D16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="7">
         <v>2020.0</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="5">
-        <v>34.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2020.0</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="6">
+        <v>45.0</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="6">
+        <v>47.0</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="6">
+        <v>51.0</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="6">
+        <v>54.0</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="6">
+        <v>56.0</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="6">
+        <v>58.0</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="6">
+        <v>59.0</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="6">
+        <v>64.0</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="6">
+        <v>67.0</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="6">
+        <v>71.0</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="6">
+        <v>73.0</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="6">
+        <v>75.0</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="6">
+        <v>77.0</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="C30" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="6">
+        <v>84.0</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="6">
+        <v>86.0</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="6">
+        <v>91.0</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="6">
+        <v>92.0</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="6">
+        <v>94.0</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="6">
+        <v>99.0</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="F36" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="6">
+        <v>100.0</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="6">
+        <v>102.0</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="6">
+        <v>104.0</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="6">
+        <v>108.0</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="6">
+        <v>112.0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="6">
+        <v>116.0</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="5">
-        <v>47.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="5">
-        <v>51.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="5">
-        <v>54.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="5">
-        <v>56.0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="5">
-        <v>58.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="5">
-        <v>59.0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="5">
-        <v>64.0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="5">
-        <v>67.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="5">
-        <v>71.0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="5">
-        <v>73.0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="5">
-        <v>75.0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="5">
-        <v>77.0</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="5">
-        <v>84.0</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="5">
-        <v>86.0</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="5">
-        <v>91.0</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="5">
-        <v>92.0</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="5">
-        <v>94.0</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="5">
-        <v>99.0</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="5">
-        <v>102.0</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="5">
-        <v>104.0</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="5">
-        <v>108.0</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="6">
+      <c r="F42" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="6">
+        <v>118.0</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="5">
-        <v>112.0</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="6">
+      <c r="D43" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="6">
+        <v>121.0</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="5">
-        <v>116.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="6">
+      <c r="D44" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="6">
+        <v>126.0</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="5">
-        <v>118.0</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C43" s="6">
+      <c r="D45" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="6">
+        <v>128.0</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="5">
-        <v>121.0</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="6">
+      <c r="D46" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="6">
+        <v>132.0</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="5">
-        <v>126.0</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="5">
-        <v>128.0</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C46" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="5">
-        <v>132.0</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>16</v>
+      <c r="G47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1"/>
@@ -5951,1349 +5945,1349 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2016.0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="6">
+        <v>17.0</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="6">
+        <v>19.0</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="6">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="6">
+        <v>23.0</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="6">
+        <v>31.0</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="6">
+        <v>33.0</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="6">
+        <v>45.0</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="6">
+        <v>47.0</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="6">
+        <v>51.0</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="6">
+        <v>54.0</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="6">
+        <v>56.0</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2015.0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6">
-        <v>2016.0</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="5">
-        <v>9.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2017.0</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2018.0</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="5">
-        <v>21.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="5">
-        <v>23.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2019.0</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="5">
-        <v>31.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2020.0</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="5">
-        <v>33.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2020.0</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="5">
-        <v>34.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2020.0</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="G22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="6">
+        <v>58.0</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="6">
+        <v>59.0</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="6">
+        <v>64.0</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="6">
+        <v>67.0</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="6">
+        <v>71.0</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="6">
+        <v>73.0</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="6">
+        <v>75.0</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="6">
+        <v>77.0</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="C30" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="6">
+        <v>84.0</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="6">
+        <v>86.0</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="6">
+        <v>91.0</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="6">
+        <v>92.0</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="6">
+        <v>94.0</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="6">
+        <v>99.0</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="F36" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="6">
+        <v>100.0</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="6">
+        <v>102.0</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="6">
+        <v>104.0</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="6">
+        <v>108.0</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="6">
+        <v>112.0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="6">
+        <v>116.0</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="5">
-        <v>47.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="5">
-        <v>51.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="5">
-        <v>54.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="5">
-        <v>56.0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="5">
-        <v>58.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="5">
-        <v>59.0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2021.0</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="5">
-        <v>64.0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="5">
-        <v>67.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="5">
-        <v>71.0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="6">
-        <v>2022.0</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="5">
-        <v>73.0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="5">
-        <v>75.0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="5">
-        <v>77.0</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="5">
-        <v>84.0</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="5">
-        <v>86.0</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="5">
-        <v>91.0</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="5">
-        <v>92.0</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="5">
-        <v>94.0</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="5">
-        <v>99.0</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="5">
-        <v>100.0</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="5">
-        <v>102.0</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="5">
-        <v>104.0</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="5">
-        <v>108.0</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="6">
+      <c r="F42" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="6">
+        <v>118.0</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="5">
-        <v>112.0</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="6">
+      <c r="D43" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="6">
+        <v>121.0</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="5">
-        <v>116.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="6">
+      <c r="D44" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="6">
+        <v>126.0</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="5">
-        <v>118.0</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C43" s="6">
+      <c r="D45" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="6">
+        <v>128.0</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="5">
-        <v>121.0</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="6">
+      <c r="D46" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="6">
+        <v>132.0</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="7">
         <v>2025.0</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="5">
-        <v>126.0</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="5">
-        <v>128.0</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C46" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="5">
-        <v>132.0</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>16</v>
+      <c r="G47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1"/>
